--- a/data/trans_dic/P56$familiar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,86</t>
+          <t>0,0; 40,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 36,95</t>
+          <t>4,32; 34,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 33,51</t>
+          <t>4,17; 34,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 50,57</t>
+          <t>24,12; 52,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 43,59</t>
+          <t>8,62; 43,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 36,89</t>
+          <t>11,55; 36,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 24,2</t>
+          <t>4,91; 25,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,96; 64,91</t>
+          <t>44,74; 63,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 35,01</t>
+          <t>7,96; 34,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 31,96</t>
+          <t>11,48; 32,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 24,38</t>
+          <t>6,38; 23,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,69; 56,48</t>
+          <t>40,47; 56,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 36,93</t>
+          <t>10,33; 38,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,69; 44,41</t>
+          <t>18,9; 43,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 29,43</t>
+          <t>9,93; 30,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,87; 64,7</t>
+          <t>46,09; 64,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 27,23</t>
+          <t>8,36; 27,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,98; 39,25</t>
+          <t>24,04; 39,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,76; 38,59</t>
+          <t>21,02; 38,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,96; 61,31</t>
+          <t>50,68; 60,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,23; 26,99</t>
+          <t>12,41; 27,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,94; 38,07</t>
+          <t>25,27; 37,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,31; 33,25</t>
+          <t>19,9; 34,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,09; 60,41</t>
+          <t>51,11; 59,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 33,76</t>
+          <t>11,73; 33,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 38,07</t>
+          <t>17,48; 38,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,9</t>
+          <t>9,72; 26,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,71; 57,66</t>
+          <t>42,14; 57,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,87; 28,15</t>
+          <t>10,32; 27,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,83; 36,33</t>
+          <t>23,77; 36,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,22; 32,66</t>
+          <t>17,83; 32,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,73; 60,64</t>
+          <t>50,72; 60,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 26,35</t>
+          <t>12,78; 26,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,71; 34,3</t>
+          <t>22,94; 34,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,63; 28,86</t>
+          <t>17,31; 29,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,47; 57,9</t>
+          <t>49,81; 58,07</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>43656</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5000</t>
+          <t>0; 5198</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>949; 7917</t>
+          <t>926; 7486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>859; 7069</t>
+          <t>879; 7211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6532; 14994</t>
+          <t>7474; 16310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1933; 9619</t>
+          <t>1903; 9695</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4797; 15543</t>
+          <t>4869; 15546</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2104; 9965</t>
+          <t>2021; 10613</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23829; 34400</t>
+          <t>26601; 37915</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2838; 12230</t>
+          <t>2781; 12127</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7746; 20317</t>
+          <t>7295; 20732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3978; 15182</t>
+          <t>3971; 14436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33628; 46681</t>
+          <t>36602; 51246</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40146</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>111666</t>
+          <t>120540</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>151812</t>
+          <t>162801</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4302; 13079</t>
+          <t>3659; 13588</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10670; 25347</t>
+          <t>10785; 25036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5099; 15009</t>
+          <t>5063; 15364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33211; 46846</t>
+          <t>35763; 49847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5917; 19463</t>
+          <t>5979; 19620</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40749; 64019</t>
+          <t>39204; 63610</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27109; 50402</t>
+          <t>27453; 50173</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>102895; 121412</t>
+          <t>109442; 131256</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13068; 28849</t>
+          <t>13266; 29712</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54916; 83823</t>
+          <t>55636; 83043</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35073; 60385</t>
+          <t>36132; 63377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>140879; 163376</t>
+          <t>150045; 175922</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>140834</t>
+          <t>152671</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>191987</t>
+          <t>206457</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4961; 16299</t>
+          <t>5663; 16148</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12593; 29885</t>
+          <t>13724; 29980</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7036; 18674</t>
+          <t>7008; 19030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43587; 58844</t>
+          <t>45758; 62271</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10165; 26329</t>
+          <t>9655; 25607</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46863; 74566</t>
+          <t>48778; 74875</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31293; 56105</t>
+          <t>30624; 55836</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>129858; 152218</t>
+          <t>139710; 165284</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17788; 37377</t>
+          <t>18120; 37429</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67265; 97332</t>
+          <t>65087; 96671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42987; 70377</t>
+          <t>42208; 71623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>178211; 204443</t>
+          <t>191274; 222974</t>
         </is>
       </c>
     </row>
